--- a/계산모델_엑셀/공정모델.xlsx
+++ b/계산모델_엑셀/공정모델.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,6 +115,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,7 +197,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -358,6 +361,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -383,6 +389,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -408,6 +417,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -762,7 +774,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>① kV직선(기울기 s, 최적 kV*) ← Phase A  ② void 최소픽셀 N_target ← Phase B  ③ 범프검출 하한 N_detect ← B3·B4  ④ 최소 Frame ← F1·F2  ⑤ tact 계수 a,b ← 전 런 타임스탬프</t>
+          <t>① kV직선(기울기 s, 최적 kV*) ← Phase A  ② void 최소픽셀 N_target ← Phase B  ③ 범프검출 하한 N_detect ← B3·B4  ④ 최소 Frame ← F1·F2  ⑤ 검사시간 계수 a,b ← 전 런 타임스탬프  ⑥ 두꺼운 범프 최적 W ← PhaseW (W는 고정 아님)</t>
         </is>
       </c>
     </row>
@@ -774,7 +786,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>kV: 창 밖(55·65) 실측으로 범위 제한 후 직선에 3점째만 추가 / R: 로그 등간격 5점, 2.0은 미지영역 / Frame: √F 물리라 배수 3점 / 158µm: 데이터 0 → 2점 직선+이식검증 1점</t>
+          <t>kV: 창 밖(55·65) 실측으로 범위 제한 후 직선에 3점째만 추가 / R: 로그 등간격 5점, 2.0은 미지영역 / Frame: √F 물리라 배수 3점 / 158µm: 데이터 0 → 2점 직선(60·63kV)+이식검증 1점 / W: 158µm에서 깜빡임void·σ가 최소가 되는 값 탐색(26µm는 둔감→4W)</t>
         </is>
       </c>
     </row>
@@ -798,7 +810,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>17~19런 (P0 2~4, A 2~4, B 6~7, F 2, T 1, C 2)</t>
+          <t>26~28런 (P0 2~4, A 2~4, B 6~7, F 2, T 1, C 2, W 9(158µm)). 얇은 범프는 W 고정(4W), 두꺼운 범프만 W 스윕.</t>
         </is>
       </c>
     </row>
@@ -813,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -909,6 +921,11 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -955,6 +972,9 @@
       <c r="M2" s="6" t="n"/>
       <c r="N2" s="6" t="n"/>
       <c r="O2" s="5" t="n"/>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1001,6 +1021,9 @@
       <c r="M3" s="6" t="n"/>
       <c r="N3" s="6" t="n"/>
       <c r="O3" s="5" t="n"/>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1047,6 +1070,9 @@
       <c r="M4" s="6" t="n"/>
       <c r="N4" s="6" t="n"/>
       <c r="O4" s="5" t="n"/>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1093,6 +1119,9 @@
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="6" t="n"/>
       <c r="O5" s="5" t="n"/>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1139,6 +1168,9 @@
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="5" t="n"/>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1187,6 +1219,9 @@
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="5" t="n"/>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1235,6 +1270,9 @@
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="5" t="n"/>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1283,6 +1321,9 @@
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
       <c r="O9" s="5" t="n"/>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1331,6 +1372,9 @@
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="5" t="n"/>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1379,6 +1423,9 @@
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="5" t="n"/>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1427,6 +1474,9 @@
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
       <c r="O12" s="5" t="n"/>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1475,6 +1525,9 @@
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
       <c r="O13" s="5" t="n"/>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1523,6 +1576,9 @@
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
       <c r="O14" s="5" t="n"/>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1571,6 +1627,11 @@
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
       <c r="O15" s="5" t="n"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>모델W</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1623,6 +1684,9 @@
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
       <c r="O16" s="5" t="n"/>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1673,6 +1737,278 @@
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="5" t="n"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>모델W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W1~3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>모델R</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>158</v>
+      </c>
+      <c r="J18">
+        <f>IFERROR(H18/I18,"")</f>
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>기준점 3반복 — 깜빡임void·void%σ</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>모델R</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>158</v>
+      </c>
+      <c r="J19">
+        <f>IFERROR(H19/I19,"")</f>
+        <v/>
+      </c>
+      <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>저측(악화 방향 확인)</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>모델R</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>32</v>
+      </c>
+      <c r="I20" t="n">
+        <v>158</v>
+      </c>
+      <c r="J20">
+        <f>IFERROR(H20/I20,"")</f>
+        <v/>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>중간점</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W6~8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>모델R</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>32</v>
+      </c>
+      <c r="I21" t="n">
+        <v>158</v>
+      </c>
+      <c r="J21">
+        <f>IFERROR(H21/I21,"")</f>
+        <v/>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>고측 3반복 + 블러 가드</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>모델R</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>158</v>
+      </c>
+      <c r="J22">
+        <f>IFERROR(H22/I22,"")</f>
+        <v/>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>W·F 교환검증: (4W,F32)와 void% 비교</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>8(허용시)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1832,10 +2168,27 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>W 최적값 (158µm)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>수동판독</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>PhaseW: 깜빡임 void=0 &amp; void%σ 최소가 되는 W (얇은 26µm는 4W 고정)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>→ 확정된 계수는 Recipe_Model.xlsx '보정계수' 시트에 옮겨 적으면 레시피 모델 완성</t>
+          <t>→ 확정된 계수는 레시피모델.xlsx '보정계수' 시트에 옮겨 적으면 레시피 모델 완성</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델.xlsx
+++ b/계산모델_엑셀/공정모델.xlsx
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -811,6 +811,18 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>26~28런 (P0 2~4, A 2~4, B 6~7, F 2, T 1, C 2, W 9(158µm)). 얇은 범프는 W 고정(4W), 두꺼운 범프만 W 스윕.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>shot·검사량</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>R이 FOV(촬영영역)를 정해 shot당 범프 수 ∝ R². 검사시간 ∝ shot 수. 품질 실험은 '가장 작은 R에서도 1 shot에 드는 중앙 ~50개 범프'만 추적해 shot 교란 제거. 별도 대조(S1·S2: 같은 R, 1 shot vs 6타일)로 타일 자체 영향 검증. 최소 표본 ~50개.</t>
         </is>
       </c>
     </row>
@@ -825,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -926,6 +938,16 @@
           <t>W</t>
         </is>
       </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
+          <t>검사범프수</t>
+        </is>
+      </c>
+      <c r="R1" s="12" t="inlineStr">
+        <is>
+          <t>shot수</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -975,6 +997,12 @@
       <c r="P2" t="n">
         <v>4</v>
       </c>
+      <c r="Q2" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1024,6 +1052,12 @@
       <c r="P3" t="n">
         <v>4</v>
       </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1073,6 +1107,12 @@
       <c r="P4" t="n">
         <v>4</v>
       </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1122,6 +1162,12 @@
       <c r="P5" t="n">
         <v>4</v>
       </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1171,6 +1217,12 @@
       <c r="P6" t="n">
         <v>4</v>
       </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1222,6 +1274,12 @@
       <c r="P7" t="n">
         <v>4</v>
       </c>
+      <c r="Q7" t="n">
+        <v>50</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1273,6 +1331,12 @@
       <c r="P8" t="n">
         <v>4</v>
       </c>
+      <c r="Q8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1324,6 +1388,12 @@
       <c r="P9" t="n">
         <v>4</v>
       </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1375,6 +1445,12 @@
       <c r="P10" t="n">
         <v>4</v>
       </c>
+      <c r="Q10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1426,6 +1502,12 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
+      <c r="Q11" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1477,6 +1559,12 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
+      <c r="Q12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1528,6 +1616,12 @@
       <c r="P13" t="n">
         <v>4</v>
       </c>
+      <c r="Q13" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1579,6 +1673,12 @@
       <c r="P14" t="n">
         <v>4</v>
       </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1630,6 +1730,14 @@
       <c r="P15" t="inlineStr">
         <is>
           <t>모델W</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>300</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>R따라</t>
         </is>
       </c>
     </row>
@@ -1687,6 +1795,14 @@
       <c r="P16" t="n">
         <v>4</v>
       </c>
+      <c r="Q16" t="n">
+        <v>300</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>R따라</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1742,6 +1858,14 @@
           <t>모델W</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>300</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>R따라</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1795,6 +1919,12 @@
       <c r="P18" t="n">
         <v>4</v>
       </c>
+      <c r="Q18" t="n">
+        <v>50</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1848,6 +1978,12 @@
       <c r="P19" t="n">
         <v>3</v>
       </c>
+      <c r="Q19" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1901,6 +2037,12 @@
       <c r="P20" t="n">
         <v>5</v>
       </c>
+      <c r="Q20" t="n">
+        <v>50</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1954,6 +2096,12 @@
       <c r="P21" t="n">
         <v>6</v>
       </c>
+      <c r="Q21" t="n">
+        <v>50</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2008,6 +2156,126 @@
         <is>
           <t>8(허용시)</t>
         </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>32</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26</v>
+      </c>
+      <c r="J23">
+        <f>IFERROR(H23/I23,"")</f>
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>단일 shot 기준</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>300</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>32</v>
+      </c>
+      <c r="I24" t="n">
+        <v>26</v>
+      </c>
+      <c r="J24">
+        <f>IFERROR(H24/I24,"")</f>
+        <v/>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>같은 R·범프 6타일 → 타일 순수효과</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>300</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2422,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tact 계수 a, b</t>
+          <t>tact 계수 a, b (shot 기반)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -2164,7 +2432,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>전 런의 tact를 x=(die면적/R²)·F 에 회귀: 기울기=a, 절편=b → Recipe_Model 보정계수에 기입</t>
+          <t>tact = a·(shot수·Frame) + b 로 회귀(기울기=a, 절편=b). shot수=ROUNDUP(목표범프/‌(R²에 비례하는 shot당범프)). → 레시피모델.xlsx '보정계수'에 기입</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델.xlsx
+++ b/계산모델_엑셀/공정모델.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>R이 FOV(촬영영역)를 정해 shot당 범프 수 ∝ R². 검사시간 ∝ shot 수. 품질 실험은 '가장 작은 R에서도 1 shot에 드는 중앙 ~50개 범프'만 추적해 shot 교란 제거. 별도 대조(S1·S2: 같은 R, 1 shot vs 6타일)로 타일 자체 영향 검증. 최소 표본 ~50개.</t>
+          <t>R이 FOV(촬영영역)를 정해 shot당 범프 수 ∝ R²(pitch 영향은 검사성공률 관점에서 작다고 보아 미반영). 검사시간 ∝ shot 수. 품질 실험은 '가장 작은 R에서도 1 shot에 드는 중앙 ~50개 범프'만 추적해 shot 교란 제거. 별도 대조(S1·S2: 같은 R, 1 shot vs 6타일)로 타일 자체 영향 검증. 최소 표본 ~50개. ※ R0.2→50개는 아직 미확정 예시치 — 장비 실측 후 갱신 필요.</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델.xlsx
+++ b/계산모델_엑셀/공정모델.xlsx
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="5" t="n">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I22" t="n">
         <v>158</v>
